--- a/Reports/AreDifferent/decryption_heating2/pattern.xlsx
+++ b/Reports/AreDifferent/decryption_heating2/pattern.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\AreDifferent\decryption_heating2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA81FD4D-865C-46E7-BFB9-2D17403B6395}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="390" windowWidth="28440" windowHeight="12195"/>
+    <workbookView xWindow="180" yWindow="390" windowWidth="28440" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" refMode="R1C1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t>№ п/п</t>
   </si>
@@ -226,39 +232,18 @@
     <t>$this-&gt;H['name_organization']</t>
   </si>
   <si>
-    <t>Утверждаю :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">по жилищно-коммунальному хозяйству </t>
-  </si>
-  <si>
-    <t>___________________   С.В.Смараков</t>
-  </si>
-  <si>
     <t>Справка по расчету субсидии на отопление</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Приложение  к Соглашению № 40-юр  с 19.02.2024 </t>
-  </si>
-  <si>
-    <t>И. о.заместителя Главы Беловского городского округа</t>
-  </si>
-  <si>
-    <t>(на осн.доверенности № 1/1987-8 от 22.04.2024)</t>
-  </si>
-  <si>
-    <t>"______"_________________   2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -430,30 +415,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -489,6 +450,30 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -496,6 +481,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -785,9 +778,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR23"/>
-  <sheetFormatPr defaultRowHeight="12" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="7" style="4" customWidth="1"/>
@@ -807,663 +800,649 @@
     <col min="49" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="25"/>
-      <c r="AN1" s="25"/>
-      <c r="AO1" s="26"/>
-      <c r="AP1" s="26"/>
-      <c r="AQ1" s="26"/>
-      <c r="AR1" s="26"/>
-    </row>
-    <row r="2" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A2" s="23"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="26"/>
-      <c r="AP2" s="26"/>
-      <c r="AQ2" s="26"/>
-      <c r="AR2" s="26"/>
-    </row>
-    <row r="3" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="35" t="s">
+    <row r="1" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="24"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="21"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="21"/>
+      <c r="AJ1" s="24"/>
+      <c r="AK1" s="24"/>
+      <c r="AL1" s="24"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
+      <c r="AR1" s="18"/>
+    </row>
+    <row r="2" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="17"/>
+      <c r="AN2" s="17"/>
+      <c r="AO2" s="18"/>
+      <c r="AP2" s="18"/>
+      <c r="AQ2" s="18"/>
+      <c r="AR2" s="18"/>
+    </row>
+    <row r="3" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="24"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="17"/>
+      <c r="AN3" s="17"/>
+      <c r="AO3" s="18"/>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="18"/>
+    </row>
+    <row r="4" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="21"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="21"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="17"/>
+      <c r="AN4" s="17"/>
+      <c r="AO4" s="18"/>
+      <c r="AP4" s="18"/>
+      <c r="AQ4" s="18"/>
+      <c r="AR4" s="18"/>
+    </row>
+    <row r="5" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="21"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="17"/>
+      <c r="AN5" s="17"/>
+      <c r="AO5" s="18"/>
+      <c r="AP5" s="18"/>
+      <c r="AQ5" s="18"/>
+      <c r="AR5" s="18"/>
+    </row>
+    <row r="6" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="21"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="21"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="24"/>
+      <c r="AM6" s="17"/>
+      <c r="AN6" s="17"/>
+      <c r="AO6" s="18"/>
+      <c r="AP6" s="18"/>
+      <c r="AQ6" s="18"/>
+      <c r="AR6" s="18"/>
+    </row>
+    <row r="7" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="21"/>
+      <c r="AJ7" s="24"/>
+      <c r="AK7" s="24"/>
+      <c r="AL7" s="24"/>
+      <c r="AM7" s="17"/>
+      <c r="AN7" s="17"/>
+      <c r="AO7" s="18"/>
+      <c r="AP7" s="18"/>
+      <c r="AQ7" s="18"/>
+      <c r="AR7" s="18"/>
+    </row>
+    <row r="8" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="21"/>
+      <c r="AH8" s="27"/>
+      <c r="AI8" s="21"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="24"/>
+      <c r="AL8" s="24"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="17"/>
+      <c r="AO8" s="18"/>
+      <c r="AP8" s="18"/>
+      <c r="AQ8" s="18"/>
+      <c r="AR8" s="18"/>
+    </row>
+    <row r="9" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="21"/>
+      <c r="AH9" s="27"/>
+      <c r="AI9" s="21"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="17"/>
+      <c r="AO9" s="18"/>
+      <c r="AP9" s="18"/>
+      <c r="AQ9" s="18"/>
+      <c r="AR9" s="18"/>
+    </row>
+    <row r="10" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="24"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="17"/>
+      <c r="AN10" s="17"/>
+      <c r="AO10" s="18"/>
+      <c r="AP10" s="18"/>
+      <c r="AQ10" s="18"/>
+      <c r="AR10" s="18"/>
+    </row>
+    <row r="11" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
+      <c r="AG11" s="24"/>
+      <c r="AH11" s="24"/>
+      <c r="AI11" s="24"/>
+      <c r="AJ11" s="24"/>
+      <c r="AK11" s="24"/>
+      <c r="AL11" s="24"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="18"/>
+      <c r="AP11" s="18"/>
+      <c r="AQ11" s="18"/>
+      <c r="AR11" s="18"/>
+    </row>
+    <row r="12" spans="1:44" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="26"/>
-    </row>
-    <row r="4" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
-      <c r="AM4" s="25"/>
-      <c r="AN4" s="25"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="26"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="26"/>
-    </row>
-    <row r="5" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A5" s="23"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="32"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="32"/>
-      <c r="AM5" s="25"/>
-      <c r="AN5" s="25"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="26"/>
-    </row>
-    <row r="6" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="32"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="32"/>
-      <c r="AM6" s="25"/>
-      <c r="AN6" s="25"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="26"/>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
-    </row>
-    <row r="7" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A7" s="23"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="32"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="32"/>
-      <c r="AA7" s="32"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="32"/>
-      <c r="AF7" s="32"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="36"/>
-      <c r="AI7" s="29"/>
-      <c r="AJ7" s="32"/>
-      <c r="AK7" s="32"/>
-      <c r="AL7" s="32"/>
-      <c r="AM7" s="25"/>
-      <c r="AN7" s="25"/>
-      <c r="AO7" s="26"/>
-      <c r="AP7" s="26"/>
-      <c r="AQ7" s="26"/>
-      <c r="AR7" s="26"/>
-    </row>
-    <row r="8" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="32"/>
-      <c r="W8" s="32"/>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="32"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI8" s="29"/>
-      <c r="AJ8" s="32"/>
-      <c r="AK8" s="32"/>
-      <c r="AL8" s="32"/>
-      <c r="AM8" s="25"/>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="26"/>
-      <c r="AP8" s="26"/>
-      <c r="AQ8" s="26"/>
-      <c r="AR8" s="26"/>
-    </row>
-    <row r="9" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A9" s="23"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="32"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="32"/>
-      <c r="AK9" s="32"/>
-      <c r="AL9" s="32"/>
-      <c r="AM9" s="25"/>
-      <c r="AN9" s="25"/>
-      <c r="AO9" s="26"/>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26"/>
-      <c r="AR9" s="26"/>
-    </row>
-    <row r="10" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="32"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="32"/>
-      <c r="AG10" s="32"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="32"/>
-      <c r="AJ10" s="32"/>
-      <c r="AK10" s="32"/>
-      <c r="AL10" s="32"/>
-      <c r="AM10" s="25"/>
-      <c r="AN10" s="25"/>
-      <c r="AO10" s="26"/>
-      <c r="AP10" s="26"/>
-      <c r="AQ10" s="26"/>
-      <c r="AR10" s="26"/>
-    </row>
-    <row r="11" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A11" s="23"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="32"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="32"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="32"/>
-      <c r="AG11" s="32"/>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="32"/>
-      <c r="AJ11" s="32"/>
-      <c r="AK11" s="32"/>
-      <c r="AL11" s="32"/>
-      <c r="AM11" s="25"/>
-      <c r="AN11" s="25"/>
-      <c r="AO11" s="26"/>
-      <c r="AP11" s="26"/>
-      <c r="AQ11" s="26"/>
-      <c r="AR11" s="26"/>
-    </row>
-    <row r="12" spans="1:44" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="25"/>
-      <c r="AN12" s="25"/>
-      <c r="AO12" s="26"/>
-      <c r="AP12" s="26"/>
-      <c r="AQ12" s="26"/>
-      <c r="AR12" s="26"/>
-    </row>
-    <row r="13" spans="1:44" ht="18.75" customHeight="1">
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="30"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="18"/>
+      <c r="AP12" s="18"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="18"/>
+    </row>
+    <row r="13" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="38"/>
-      <c r="AB13" s="38"/>
-      <c r="AC13" s="38"/>
-      <c r="AD13" s="38"/>
-      <c r="AE13" s="38"/>
-      <c r="AF13" s="38"/>
-      <c r="AG13" s="38"/>
-      <c r="AH13" s="38"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="38"/>
-      <c r="AK13" s="38"/>
-      <c r="AL13" s="38"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="30"/>
+      <c r="AD13" s="30"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="30"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="30"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
     </row>
-    <row r="14" spans="1:44" ht="18.75" customHeight="1">
+    <row r="14" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="18"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="18"/>
-      <c r="AD14" s="18"/>
-      <c r="AE14" s="18"/>
-      <c r="AF14" s="18"/>
-      <c r="AG14" s="18"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
-      <c r="AK14" s="18"/>
-      <c r="AL14" s="18"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="32"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="32"/>
+      <c r="AF14" s="32"/>
+      <c r="AG14" s="32"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="32"/>
+      <c r="AJ14" s="32"/>
+      <c r="AK14" s="32"/>
+      <c r="AL14" s="32"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
     </row>
-    <row r="15" spans="1:44" ht="18.75" customHeight="1">
+    <row r="15" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1505,7 +1484,7 @@
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
     </row>
-    <row r="16" spans="1:44" ht="18.75" customHeight="1">
+    <row r="16" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1547,7 +1526,7 @@
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
     </row>
-    <row r="17" spans="1:40" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row r="17" spans="1:40" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1589,255 +1568,255 @@
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
     </row>
-    <row r="18" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1">
-      <c r="B18" s="20" t="s">
+    <row r="18" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="22" t="s">
+      <c r="K18" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L18" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="17" t="s">
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="15" t="s">
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="V18" s="17" t="s">
+      <c r="V18" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="17"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="38"/>
+      <c r="Z18" s="38"/>
+      <c r="AA18" s="38"/>
+      <c r="AB18" s="38"/>
+      <c r="AC18" s="38"/>
       <c r="AD18" s="7"/>
       <c r="AE18" s="7"/>
-      <c r="AF18" s="15" t="s">
+      <c r="AF18" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15" t="s">
+      <c r="AG18" s="33"/>
+      <c r="AH18" s="33"/>
+      <c r="AI18" s="33"/>
+      <c r="AJ18" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
+      <c r="AK18" s="33"/>
+      <c r="AL18" s="33"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
     </row>
-    <row r="19" spans="1:40" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B19" s="20"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15" t="s">
+    <row r="19" spans="1:40" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="16" t="s">
+      <c r="K19" s="37"/>
+      <c r="L19" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M19" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="N19" s="16" t="s">
+      <c r="N19" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="O19" s="16" t="s">
+      <c r="O19" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="P19" s="17" t="s">
+      <c r="P19" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="Q19" s="17" t="s">
+      <c r="Q19" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="R19" s="17" t="s">
+      <c r="R19" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="S19" s="17" t="s">
+      <c r="S19" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="T19" s="17"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="17" t="s">
+      <c r="T19" s="38"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="W19" s="17" t="s">
+      <c r="W19" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="38"/>
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
-      <c r="AF19" s="15" t="s">
+      <c r="AF19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="AG19" s="15" t="s">
+      <c r="AG19" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AH19" s="15"/>
-      <c r="AI19" s="15"/>
-      <c r="AJ19" s="15" t="s">
+      <c r="AH19" s="33"/>
+      <c r="AI19" s="33"/>
+      <c r="AJ19" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="AK19" s="15" t="s">
+      <c r="AK19" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="AL19" s="15" t="s">
+      <c r="AL19" s="33" t="s">
         <v>34</v>
       </c>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="1:40" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B20" s="20"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15" t="s">
+    <row r="20" spans="1:40" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="33" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="6"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17" t="s">
+      <c r="K20" s="37"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="T20" s="17" t="s">
+      <c r="T20" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="U20" s="15"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17" t="s">
+      <c r="U20" s="33"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38" t="s">
         <v>35</v>
       </c>
       <c r="X20" s="8"/>
       <c r="Y20" s="8"/>
-      <c r="Z20" s="17" t="s">
+      <c r="Z20" s="38" t="s">
         <v>25</v>
       </c>
       <c r="AA20" s="7"/>
       <c r="AB20" s="7"/>
-      <c r="AC20" s="17" t="s">
+      <c r="AC20" s="38" t="s">
         <v>26</v>
       </c>
       <c r="AD20" s="7"/>
       <c r="AE20" s="7"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15" t="s">
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="AH20" s="15" t="s">
+      <c r="AH20" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="AI20" s="15" t="s">
+      <c r="AI20" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="AJ20" s="15"/>
-      <c r="AK20" s="15"/>
-      <c r="AL20" s="15"/>
+      <c r="AJ20" s="33"/>
+      <c r="AK20" s="33"/>
+      <c r="AL20" s="33"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
     </row>
-    <row r="21" spans="1:40" s="4" customFormat="1" ht="113.25" customHeight="1">
-      <c r="B21" s="20"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+    <row r="21" spans="1:40" s="4" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
       <c r="J21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="22"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
       <c r="X21" s="8"/>
       <c r="Y21" s="8"/>
-      <c r="Z21" s="17"/>
+      <c r="Z21" s="38"/>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="17"/>
+      <c r="AC21" s="38"/>
       <c r="AD21" s="7"/>
       <c r="AE21" s="7"/>
-      <c r="AF21" s="15"/>
-      <c r="AG21" s="15"/>
-      <c r="AH21" s="15"/>
-      <c r="AI21" s="15"/>
-      <c r="AJ21" s="15"/>
-      <c r="AK21" s="15"/>
-      <c r="AL21" s="15"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33"/>
+      <c r="AH21" s="33"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="33"/>
+      <c r="AK21" s="33"/>
+      <c r="AL21" s="33"/>
       <c r="AM21" s="3"/>
       <c r="AN21" s="3"/>
     </row>
-    <row r="22" spans="1:40" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B22" s="20"/>
-      <c r="C22" s="16"/>
+    <row r="22" spans="1:40" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="9" t="s">
         <v>9</v>
       </c>
@@ -1934,9 +1913,9 @@
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
     </row>
-    <row r="23" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="20"/>
-      <c r="C23" s="16"/>
+    <row r="23" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="12">
         <v>1</v>
       </c>
@@ -2036,6 +2015,33 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="43">
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="L19:L21"/>
+    <mergeCell ref="M19:M21"/>
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="Q19:Q21"/>
+    <mergeCell ref="R19:R21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="V19:V21"/>
+    <mergeCell ref="W19:AC19"/>
+    <mergeCell ref="AF19:AF21"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="U18:U21"/>
+    <mergeCell ref="V18:AC18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="AC20:AC21"/>
+    <mergeCell ref="AG20:AG21"/>
+    <mergeCell ref="AH20:AH21"/>
+    <mergeCell ref="AI20:AI21"/>
     <mergeCell ref="B12:AL12"/>
     <mergeCell ref="B13:AL13"/>
     <mergeCell ref="B14:AL14"/>
@@ -2052,33 +2058,6 @@
     <mergeCell ref="I20:I21"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="P18:T18"/>
-    <mergeCell ref="U18:U21"/>
-    <mergeCell ref="V18:AC18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="W20:W21"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="AC20:AC21"/>
-    <mergeCell ref="AG20:AG21"/>
-    <mergeCell ref="AH20:AH21"/>
-    <mergeCell ref="AI20:AI21"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="L19:L21"/>
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="Q19:Q21"/>
-    <mergeCell ref="R19:R21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="V19:V21"/>
-    <mergeCell ref="W19:AC19"/>
-    <mergeCell ref="AF19:AF21"/>
-    <mergeCell ref="AG19:AI19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2086,9 +2065,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2096,9 +2075,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
